--- a/AAII_Financials/Quarterly/NWSGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWSGY_QTR_FIN.xlsx
@@ -2244,10 +2244,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>34400</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
-        <v>34400</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
@@ -2291,10 +2291,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5593300</v>
+        <v>5560000</v>
       </c>
       <c r="E46" s="3">
-        <v>5595300</v>
+        <v>5562000</v>
       </c>
       <c r="F46" s="3">
         <v>5449300</v>
@@ -2573,10 +2573,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1024300</v>
+        <v>1057600</v>
       </c>
       <c r="E52" s="3">
-        <v>1024700</v>
+        <v>1057900</v>
       </c>
       <c r="F52" s="3">
         <v>856200</v>
@@ -2987,10 +2987,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12525000</v>
+        <v>1503100</v>
       </c>
       <c r="E62" s="3">
-        <v>12529500</v>
+        <v>1503600</v>
       </c>
       <c r="F62" s="3">
         <v>15800</v>
